--- a/lecNote/01_python/ch10_11.xlsx
+++ b/lecNote/01_python/ch10_11.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\01_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EB66DC-1839-4530-B90D-A68C32E7E7CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7CA9F4-FEE0-457D-9F0E-6A0645E4CBB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" activeTab="1" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" activeTab="2" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
   </bookViews>
   <sheets>
     <sheet name="비트" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2 (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="변경전a" sheetId="2" r:id="rId2"/>
+    <sheet name="변경후a" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>16진수</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -153,6 +153,10 @@
   </si>
   <si>
     <t>8승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0, 1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -295,7 +299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -330,6 +334,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1411,9 +1421,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
+      <c r="A3" s="10"/>
       <c r="B3" s="5">
         <v>0</v>
       </c>
@@ -1471,14 +1479,12 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>12</v>
+      <c r="A4" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="A5" s="12"/>
       <c r="B5" s="5">
         <v>0</v>
       </c>
@@ -1536,7 +1542,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5">
@@ -1565,9 +1571,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>16</v>
-      </c>
+      <c r="A7" s="13"/>
       <c r="B7" s="5">
         <v>0</v>
       </c>
@@ -1792,6 +1796,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lecNote/01_python/ch10_11.xlsx
+++ b/lecNote/01_python/ch10_11.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\01_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7CA9F4-FEE0-457D-9F0E-6A0645E4CBB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F954BFAB-911C-4F5B-B7D8-84FB4FEC7754}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" activeTab="2" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" activeTab="3" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
   </bookViews>
   <sheets>
     <sheet name="비트" sheetId="1" r:id="rId1"/>
     <sheet name="변경전a" sheetId="2" r:id="rId2"/>
     <sheet name="변경후a" sheetId="3" r:id="rId3"/>
+    <sheet name="기초통계" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>16진수</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -157,6 +158,34 @@
   </si>
   <si>
     <t>0, 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A편차들</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A편차제곱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B편차들</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B편차제곱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-분산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>표준편차</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -167,7 +196,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +223,24 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -299,7 +346,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -342,12 +389,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1803,4 +1864,207 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DBE60AF-C2C0-4C1A-B041-EA122556C749}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <f>$B$7-B2</f>
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <f>C2*C2</f>
+        <v>100</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <f>$E$7-E2</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <f>F2*F2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <f t="shared" ref="C3:C6" si="0">$B$7-B3</f>
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D6" si="1">C3*C3</f>
+        <v>100</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F6" si="2">$E$7-E3</f>
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="2">
+        <f>F3*F3</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" ref="G4:G6" si="3">F4*F4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>-12</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+      <c r="E6" s="2">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2">
+        <f>AVERAGE(B2:B6)</f>
+        <v>10</v>
+      </c>
+      <c r="C7" s="2">
+        <f>AVERAGE(C2:C6)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <f>AVERAGE(D2:D6)</f>
+        <v>81.599999999999994</v>
+      </c>
+      <c r="E7" s="2">
+        <f>AVERAGE(E2:E6)</f>
+        <v>9</v>
+      </c>
+      <c r="F7" s="2">
+        <f>AVERAGE(F2:F6)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <f>AVERAGE(G2:G6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="16">
+        <f>SQRT(D7)</f>
+        <v>9.0332718325089711</v>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16">
+        <f>SQRT(G7)</f>
+        <v>0.70710678118654757</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/lecNote/01_python/ch10_11.xlsx
+++ b/lecNote/01_python/ch10_11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\01_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F954BFAB-911C-4F5B-B7D8-84FB4FEC7754}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0EA7F-728D-4818-9183-B18C71A16D8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" activeTab="3" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
   </bookViews>
   <sheets>
     <sheet name="비트" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>16진수</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -186,6 +186,38 @@
   </si>
   <si>
     <t>표준편차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6승</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -196,7 +228,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +278,22 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,7 +303,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -340,13 +388,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -383,12 +476,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -397,6 +484,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,21 +825,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C77E24F-86AE-4A8A-A7CF-3B6D961B2A89}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="3.5" style="2"/>
+    <col min="12" max="12" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -750,8 +883,32 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="19">
+        <v>0</v>
+      </c>
+      <c r="K2" s="20">
+        <v>0</v>
+      </c>
+      <c r="L2" s="20">
+        <v>0</v>
+      </c>
+      <c r="M2" s="20">
+        <v>0</v>
+      </c>
+      <c r="N2" s="20">
+        <v>0</v>
+      </c>
+      <c r="O2" s="20">
+        <v>0</v>
+      </c>
+      <c r="P2" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -771,7 +928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -791,7 +948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -811,7 +968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -831,7 +988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -851,7 +1008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -871,7 +1028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -891,7 +1048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -911,7 +1068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -931,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -951,7 +1108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -971,7 +1128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -991,7 +1148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1011,7 +1168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1034,6 +1191,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1540,12 +1698,12 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
+      <c r="A5" s="15"/>
       <c r="B5" s="5">
         <v>0</v>
       </c>
@@ -1603,7 +1761,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5">
@@ -1632,7 +1790,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="5">
         <v>0</v>
       </c>
@@ -2021,44 +2179,44 @@
         <v>34</v>
       </c>
       <c r="B7" s="2">
-        <f>AVERAGE(B2:B6)</f>
+        <f t="shared" ref="B7:G7" si="4">AVERAGE(B2:B6)</f>
         <v>10</v>
       </c>
       <c r="C7" s="2">
-        <f>AVERAGE(C2:C6)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="14">
-        <f>AVERAGE(D2:D6)</f>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" si="4"/>
         <v>81.599999999999994</v>
       </c>
       <c r="E7" s="2">
-        <f>AVERAGE(E2:E6)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="F7" s="2">
-        <f>AVERAGE(F2:F6)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="14">
-        <f>AVERAGE(G2:G6)</f>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="14">
         <f>SQRT(D7)</f>
         <v>9.0332718325089711</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16">
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14">
         <f>SQRT(G7)</f>
         <v>0.70710678118654757</v>
       </c>

--- a/lecNote/01_python/ch10_11.xlsx
+++ b/lecNote/01_python/ch10_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\01_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0EA7F-728D-4818-9183-B18C71A16D8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB7028D-0448-4E5A-AEBF-CE629A152B6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17775" windowHeight="9705" xr2:uid="{9C313DC6-B42D-4FE4-9E1F-FBF1840BC50D}"/>
   </bookViews>
@@ -497,14 +497,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -829,7 +829,7 @@
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="3.5" style="2"/>
-    <col min="12" max="12" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="20">
         <v>0</v>
@@ -946,6 +946,10 @@
       </c>
       <c r="G4" s="2">
         <v>2</v>
+      </c>
+      <c r="K4">
+        <f>2^7 -1</f>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
